--- a/data/trans_bre/P7_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P7_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 21,49</t>
+          <t>13,47; 20,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,95</t>
+          <t>7,66; 16,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 17,18</t>
+          <t>7,97; 17,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 17,1</t>
+          <t>7,1; 17,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,23; 72,73</t>
+          <t>39,47; 69,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,86; 49,43</t>
+          <t>20,07; 49,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,06; 56,95</t>
+          <t>22,75; 57,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 46,35</t>
+          <t>16,79; 47,21</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,99</t>
+          <t>5,22; 9,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,28</t>
+          <t>3,77; 8,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,13</t>
+          <t>2,4; 7,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 7,45</t>
+          <t>-1,43; 7,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,2; 147,43</t>
+          <t>59,19; 141,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,13; 89,8</t>
+          <t>35,51; 94,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,46; 65,69</t>
+          <t>19,03; 66,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 73,1</t>
+          <t>-8,32; 74,12</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 10,33</t>
+          <t>2,16; 10,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 5,34</t>
+          <t>-2,36; 5,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,81</t>
+          <t>0,94; 7,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,66</t>
+          <t>-3,36; 3,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,51; 156,17</t>
+          <t>19,79; 164,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 117,4</t>
+          <t>-28,82; 134,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 175,99</t>
+          <t>12,04; 181,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 29,77</t>
+          <t>-27,2; 35,44</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 14,89</t>
+          <t>10,9; 15,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,04</t>
+          <t>7,81; 11,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,14</t>
+          <t>6,27; 10,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,37</t>
+          <t>1,71; 9,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,22; 100,58</t>
+          <t>65,49; 101,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,63; 77,98</t>
+          <t>44,77; 76,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,45; 68,54</t>
+          <t>37,35; 68,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 69,27</t>
+          <t>11,65; 66,45</t>
         </is>
       </c>
     </row>
